--- a/data/spectra/2_PHENTL_3s_2_TAIMETHYLENE_INDOLE__graph-291.xlsx
+++ b/data/spectra/2_PHENTL_3s_2_TAIMETHYLENE_INDOLE__graph-291.xlsx
@@ -567,7 +567,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Digitization F1 = 0.94</t>
+          <t>Digitization F1 = 0.964</t>
         </is>
       </c>
     </row>
